--- a/New folder/views/fuel_usage_by_company.xlsx
+++ b/New folder/views/fuel_usage_by_company.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\EBRAHIM\database\MYSQL\cars_datasets_2025\cars_database\New folder\views\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83193C93-EDCE-443E-BEC4-3CCB85BD9E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F804A337-57EE-4D86-B99C-457A6AFAC62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{B2143E15-4FB5-4CC4-A37B-47757681027B}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="51">
   <si>
     <t>company_names</t>
   </si>
@@ -198,19 +198,29 @@
   </si>
   <si>
     <t>volvo</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -222,7 +232,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -230,23 +240,144 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="8">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.749961851863155"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -263,24 +394,28 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{3628E562-FAE9-4AEC-8E62-82E00E79E97C}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="5">
-    <queryTableFields count="4">
+  <queryTableRefresh nextId="6" unboundColumnsRight="1">
+    <queryTableFields count="5">
       <queryTableField id="1" name="company_names" tableColumnId="1"/>
       <queryTableField id="2" name="fuel_types" tableColumnId="2"/>
       <queryTableField id="3" name="fuel_usage_count" tableColumnId="3"/>
       <queryTableField id="4" name="fuel_usage_percentage" tableColumnId="4"/>
+      <queryTableField id="5" dataBound="0" tableColumnId="5"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3B23B1DB-0B2B-4154-820E-E7D891E77389}" name="fuel_usage_by_company" displayName="fuel_usage_by_company" ref="A1:D97" tableType="queryTable" totalsRowShown="0">
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{7295B226-1943-44FE-8E3A-E8B41F805C1A}" uniqueName="1" name="company_names" queryTableFieldId="1" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{A43BE3C1-D10E-43B9-A641-3F19E13E5601}" uniqueName="2" name="fuel_types" queryTableFieldId="2" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{6AB7CC91-6437-477B-BB5F-0A6E2513693A}" uniqueName="3" name="fuel_usage_count" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{03A0E12C-983C-47C5-A67C-01BA7E2636B1}" uniqueName="4" name="fuel_usage_percentage" queryTableFieldId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3B23B1DB-0B2B-4154-820E-E7D891E77389}" name="fuel_usage_by_company" displayName="fuel_usage_by_company" ref="A1:E97" tableType="queryTable" totalsRowShown="0" headerRowDxfId="3">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{7295B226-1943-44FE-8E3A-E8B41F805C1A}" uniqueName="1" name="company_names" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{A43BE3C1-D10E-43B9-A641-3F19E13E5601}" uniqueName="2" name="fuel_types" queryTableFieldId="2" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{6AB7CC91-6437-477B-BB5F-0A6E2513693A}" uniqueName="3" name="fuel_usage_count" queryTableFieldId="3" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{03A0E12C-983C-47C5-A67C-01BA7E2636B1}" uniqueName="4" name="fuel_usage_percentage" queryTableFieldId="4" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{8895B2CA-BB37-4575-ACCA-49812AED761D}" uniqueName="5" name="0" queryTableFieldId="5" dataDxfId="5">
+      <calculatedColumnFormula>IF(A2&lt;&gt;A1,MOD(E1+1,2),E1)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -603,1376 +738,1774 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730B1D51-0DE8-4314-8D4E-E465D79A8559}">
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="1.75" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="7">
         <v>7</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="7">
         <v>25.93</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="E2">
+        <f t="shared" ref="E2:E33" si="0">IF(A2&lt;&gt;A1,MOD(E1+1,2),E1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7">
         <v>20</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="7">
         <v>74.069999999999993</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="E3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <v>2</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="7">
         <v>18.18</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
+      <c r="B5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="7">
         <v>9</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="7">
         <v>81.819999999999993</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="7">
         <v>2</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="7">
         <v>9.52</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7">
+      <c r="B7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="7">
         <v>19</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="7">
         <v>90.48</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
+      <c r="B8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="7">
         <v>10</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="7">
         <v>24.39</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7">
         <v>2.44</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11">
+      <c r="B11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7">
         <v>30</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="7">
         <v>73.17</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12">
+      <c r="B12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="7">
         <v>10</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="7">
         <v>3</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="7">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14">
+      <c r="B14" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="7">
         <v>17</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="7">
         <v>85</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="7">
         <v>4</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="7">
         <v>7.02</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="7">
         <v>4</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="7">
         <v>7.02</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17">
+      <c r="B17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="7">
         <v>49</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="7">
         <v>85.96</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18">
+      <c r="B18" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="7">
         <v>8</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="7">
         <v>88.89</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
+      <c r="C19" s="7">
+        <v>1</v>
+      </c>
+      <c r="D19" s="7">
         <v>11.11</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="7">
         <v>12</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="7">
         <v>16.22</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="7">
         <v>5</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="7">
         <v>6.76</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="7">
         <v>10</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="7">
         <v>13.51</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23">
+      <c r="B23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="7">
         <v>47</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="7">
         <v>63.51</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="7">
         <v>3</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="7">
         <v>5.08</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="7">
         <v>8</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="7">
         <v>13.56</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26">
+      <c r="B26" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="7">
         <v>48</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="7">
         <v>81.36</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
+      <c r="E26">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="7">
         <v>2</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="7">
         <v>22.22</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
+      <c r="E27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28">
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="7">
         <v>7</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="7">
         <v>77.78</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
+      <c r="E28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="7">
         <v>5</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="7">
         <v>15.63</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
+      <c r="E29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
+      <c r="C30" s="7">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7">
         <v>3.13</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+      <c r="E30">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="7">
         <v>7</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="7">
         <v>21.88</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+      <c r="E31">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
+      <c r="C32" s="7">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7">
         <v>3.13</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+      <c r="E32">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33">
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="7">
         <v>18</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="7">
         <v>56.25</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+      <c r="E33">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="7">
         <v>5</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
+      <c r="E34">
+        <f t="shared" ref="E34:E65" si="1">IF(A34&lt;&gt;A33,MOD(E33+1,2),E33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="7">
         <v>44</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="7">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
+      <c r="E35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
+      <c r="C36" s="7">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+      <c r="E36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
+      <c r="C37" s="7">
+        <v>1</v>
+      </c>
+      <c r="D37" s="7">
         <v>5.26</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
+      <c r="E37">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="7">
         <v>4</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="7">
         <v>21.05</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
+      <c r="E38">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
         <v>14</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="7">
         <v>73.680000000000007</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
+      <c r="E39">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="7">
         <v>2</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="7">
         <v>2.63</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
+      <c r="E40">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C41">
-        <v>6</v>
-      </c>
-      <c r="D41">
+      <c r="C41" s="7">
+        <v>6</v>
+      </c>
+      <c r="D41" s="7">
         <v>7.89</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
+      <c r="E41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="7">
         <v>11</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="7">
         <v>14.47</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
+      <c r="E42">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43">
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
         <v>53</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="7">
         <v>69.739999999999995</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
+      <c r="E43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="7">
         <v>4</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="7">
         <v>5.26</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
+      <c r="E44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45">
+      <c r="C45" s="7">
+        <v>1</v>
+      </c>
+      <c r="D45" s="7">
         <v>4.17</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
+      <c r="E45">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46">
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
         <v>23</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="7">
         <v>95.83</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
+      <c r="E46">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="7">
         <v>3</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="7">
         <v>75</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
+      <c r="E47">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48">
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7">
         <v>25</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
+      <c r="E48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49">
+      <c r="C49" s="7">
+        <v>1</v>
+      </c>
+      <c r="D49" s="7">
         <v>25</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
+      <c r="E49">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50">
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
         <v>3</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="7">
         <v>75</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
+      <c r="E50">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="7">
         <v>11</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="7">
         <v>6.36</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
+      <c r="E51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="7">
         <v>2</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="7">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
+      <c r="E52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="7">
         <v>4</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="7">
         <v>2.31</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
+      <c r="E53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54">
+      <c r="B54" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7">
         <v>155</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="7">
         <v>89.6</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
+      <c r="E54">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55">
+      <c r="C55" s="7">
+        <v>1</v>
+      </c>
+      <c r="D55" s="7">
         <v>0.57999999999999996</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
+      <c r="E55">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56">
+      <c r="C56" s="7">
+        <v>1</v>
+      </c>
+      <c r="D56" s="7">
         <v>4.76</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
+      <c r="E56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57">
+      <c r="B57" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="7">
         <v>20</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="7">
         <v>95.24</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="1" t="s">
+      <c r="E57">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="7">
         <v>30</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="7">
         <v>25</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="1" t="s">
+      <c r="E58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="7">
         <v>2</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="7">
         <v>1.67</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="1" t="s">
+      <c r="E59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="7">
         <v>4</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="7">
         <v>3.33</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
+      <c r="E60">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="7">
         <v>2</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="7">
         <v>1.67</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
+      <c r="E61">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62">
+      <c r="B62" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="7">
         <v>80</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="7">
         <v>66.67</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
+      <c r="E62">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="7">
         <v>2</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="7">
         <v>1.67</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
+      <c r="E63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="7">
         <v>14</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="7">
         <v>8.81</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
+      <c r="E64">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C65">
-        <v>6</v>
-      </c>
-      <c r="D65">
+      <c r="C65" s="7">
+        <v>6</v>
+      </c>
+      <c r="D65" s="7">
         <v>3.77</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
+      <c r="E65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="7">
         <v>10</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="7">
         <v>6.29</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
+      <c r="E66">
+        <f t="shared" ref="E66:E97" si="2">IF(A66&lt;&gt;A65,MOD(E65+1,2),E65)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67">
+      <c r="B67" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="7">
         <v>129</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="7">
         <v>81.13</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
+      <c r="E67">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="7">
         <v>7</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="7">
         <v>12.96</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
+      <c r="E68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="7">
         <v>5</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="7">
         <v>9.26</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
+      <c r="E69">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="7">
         <v>12</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="7">
         <v>22.22</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
+      <c r="E70">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71">
+      <c r="B71" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="7">
         <v>30</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="7">
         <v>55.56</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
+      <c r="E71">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="D72">
+      <c r="C72" s="7">
+        <v>1</v>
+      </c>
+      <c r="D72" s="7">
         <v>1.04</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
+      <c r="E72">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="7">
         <v>14</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="7">
         <v>14.58</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
+      <c r="E73">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="7">
         <v>7</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="7">
         <v>7.29</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
+      <c r="E74">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="7">
         <v>4</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="7">
         <v>4.17</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
+      <c r="E75">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76">
+      <c r="B76" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="7">
         <v>70</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="7">
         <v>72.92</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="1" t="s">
+      <c r="E76">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77">
+      <c r="B77" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="7">
         <v>30</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
+      <c r="E77">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78">
+      <c r="C78" s="7">
+        <v>1</v>
+      </c>
+      <c r="D78" s="7">
         <v>2.94</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
+      <c r="E78">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="7">
         <v>14</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="7">
         <v>41.18</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
+      <c r="E79">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="7">
         <v>4</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="7">
         <v>11.76</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
+      <c r="E80">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81">
+      <c r="B81" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="7">
         <v>15</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="7">
         <v>44.12</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
+      <c r="E81">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="7">
         <v>10</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
+      <c r="E82">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="7">
         <v>7</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="7">
         <v>10.77</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
+      <c r="E83">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="7">
         <v>4</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="7">
         <v>6.15</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
+      <c r="E84">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-      <c r="D85">
+      <c r="C85" s="7">
+        <v>1</v>
+      </c>
+      <c r="D85" s="7">
         <v>1.54</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
+      <c r="E85">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="7">
         <v>19</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="7">
         <v>29.23</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
+      <c r="E86">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="7">
         <v>2</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="7">
         <v>3.08</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
+      <c r="E87">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="7">
         <v>2</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="7">
         <v>3.08</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
+      <c r="E88">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89">
+      <c r="B89" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="7">
         <v>28</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="7">
         <v>43.08</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="1" t="s">
+      <c r="E89">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-      <c r="D90">
+      <c r="C90" s="7">
+        <v>1</v>
+      </c>
+      <c r="D90" s="7">
         <v>1.54</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
+      <c r="E90">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C91">
-        <v>1</v>
-      </c>
-      <c r="D91">
+      <c r="C91" s="7">
+        <v>1</v>
+      </c>
+      <c r="D91" s="7">
         <v>1.54</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
+      <c r="E91">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="7">
         <v>34</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="7">
         <v>20.239999999999998</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="1" t="s">
+      <c r="E92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="7">
         <v>18</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="7">
         <v>10.71</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="1" t="s">
+      <c r="E93">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="7">
         <v>8</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="7">
         <v>4.76</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="1" t="s">
+      <c r="E94">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95">
+      <c r="B95" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="7">
         <v>108</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="7">
         <v>64.290000000000006</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="1" t="s">
+      <c r="E95">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="7">
         <v>12</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="7">
         <v>80</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
+      <c r="E96">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97">
+      <c r="B97" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="7">
         <v>3</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="7">
         <v>20</v>
       </c>
+      <c r="E97">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:D97">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>$E2=1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>$E2=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
